--- a/docs/assets/cases/score-cross.xlsx
+++ b/docs/assets/cases/score-cross.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,20 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>dtype</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>data_source</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
@@ -461,17 +466,18 @@
           <t>外部来源分 2</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Home Credit 2018 application_{train|test}.csv</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Normalized score from external data source</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Home Credit 2018 application_{train|test}.csv</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>归一化值（无量纲）</t>
         </is>
@@ -488,17 +494,18 @@
           <t>外部来源分 3</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Home Credit 2018 application_{train|test}.csv</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>Normalized score from external data source</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Home Credit 2018 application_{train|test}.csv</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>归一化值（无量纲）</t>
         </is>
@@ -908,7 +915,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>"c1b6eb2c-9baf-41f7-8937-c9ac486c856c"</t>
+          <t>"4178f2f6-3d7c-4583-b1da-9d4c0bce24ec"</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -28019,7 +28026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28103,11 +28110,6 @@
           <t>fit_source</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>display_name</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28168,11 +28170,6 @@
           <t>saved_definition</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>外部来源分 2</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28235,11 +28232,6 @@
           <t>saved_definition</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>外部来源分 2</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28300,11 +28292,6 @@
       <c r="P4" t="inlineStr">
         <is>
           <t>saved_definition</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>外部来源分 2</t>
         </is>
       </c>
     </row>
@@ -28367,11 +28354,6 @@
           <t>saved_definition</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>外部来源分 2</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28428,11 +28410,6 @@
           <t>saved_definition</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>外部来源分 2</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28489,11 +28466,6 @@
           <t>saved_definition</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>外部来源分 2</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28554,11 +28526,6 @@
           <t>saved_definition</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>外部来源分 3</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28621,11 +28588,6 @@
           <t>saved_definition</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>外部来源分 3</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28686,11 +28648,6 @@
       <c r="P10" t="inlineStr">
         <is>
           <t>saved_definition</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>外部来源分 3</t>
         </is>
       </c>
     </row>
@@ -28753,11 +28710,6 @@
           <t>saved_definition</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>外部来源分 3</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28814,11 +28766,6 @@
           <t>saved_definition</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>外部来源分 3</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28873,11 +28820,6 @@
       <c r="P13" t="inlineStr">
         <is>
           <t>saved_definition</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>外部来源分 3</t>
         </is>
       </c>
     </row>

--- a/docs/assets/cases/score-cross.xlsx
+++ b/docs/assets/cases/score-cross.xlsx
@@ -915,7 +915,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>"4178f2f6-3d7c-4583-b1da-9d4c0bce24ec"</t>
+          <t>"5ba145f2-6fd0-44ab-85fa-de9dee9a690c"</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/docs/assets/cases/score-cross.xlsx
+++ b/docs/assets/cases/score-cross.xlsx
@@ -915,7 +915,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>"5ba145f2-6fd0-44ab-85fa-de9dee9a690c"</t>
+          <t>"77208fb5-bb0e-424b-9ddb-3b5b24790fbd"</t>
         </is>
       </c>
       <c r="C2" t="n">
